--- a/data/trans_dic/IP11C$urgencias-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$urgencias-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y acudieron a un servicio de urgencias</t>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y acudieron a un servicio de urgencias (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,52; 100,0</t>
+          <t>27,32; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,65; 85,71</t>
+          <t>16,63; 85,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -741,32 +742,32 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,35; 91,57</t>
+          <t>49,7; 90,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37,61; 90,36</t>
+          <t>36,91; 90,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,52; 85,87</t>
+          <t>49,48; 85,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,02; 64,4</t>
+          <t>31,08; 65,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,38; 65,34</t>
+          <t>38,29; 66,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,46; 96,01</t>
+          <t>65,91; 96,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,29; 87,44</t>
+          <t>38,94; 87,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55,67; 79,76</t>
+          <t>55,37; 80,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,03; 68,04</t>
+          <t>44,24; 69,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,93; 87,18</t>
+          <t>60,48; 87,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>60,91; 95,71</t>
+          <t>62,69; 95,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,21; 70,82</t>
+          <t>50,23; 70,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,52; 62,76</t>
+          <t>45,42; 62,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67,53; 87,17</t>
+          <t>66,89; 87,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>60,94; 88,82</t>
+          <t>61,45; 90,5</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61,79; 100,0</t>
+          <t>59,65; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,34; 62,59</t>
+          <t>12,97; 62,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,41; 100,0</t>
+          <t>33,93; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,94; 61,75</t>
+          <t>9,12; 69,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,35; 66,05</t>
+          <t>24,19; 64,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,12; 90,74</t>
+          <t>29,78; 89,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,15; 100,0</t>
+          <t>27,62; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45,02; 81,13</t>
+          <t>44,43; 81,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,8; 57,83</t>
+          <t>24,85; 56,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,45; 94,37</t>
+          <t>52,68; 93,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47,46; 94,23</t>
+          <t>44,59; 94,27</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,21; 71,98</t>
+          <t>47,98; 73,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,36; 60,95</t>
+          <t>39,11; 61,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74,54; 97,15</t>
+          <t>76,05; 97,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46,66; 84,29</t>
+          <t>45,78; 84,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,93; 74,21</t>
+          <t>52,25; 74,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,34; 66,11</t>
+          <t>47,12; 65,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,69; 84,75</t>
+          <t>61,57; 84,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62,43; 93,92</t>
+          <t>61,6; 93,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53,35; 70,34</t>
+          <t>52,56; 69,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,56; 60,72</t>
+          <t>46,07; 60,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69,61; 86,64</t>
+          <t>71,28; 87,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,36; 85,54</t>
+          <t>62,85; 87,22</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y acudieron a un servicio de urgencias (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2113</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2457</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2167</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9462</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4802</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11575</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4986</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1780</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1124; 4114</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>674; 3469</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1082</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>716; 2839</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6255; 11425</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2566; 6295</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>8233; 14147</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2432</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>9990</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19861</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14021</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7388</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>25406</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>25041</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>23681</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>12484</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>35396</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>44901</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>37702</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>19873</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6541; 13842</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14533; 25128</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>10875; 15858</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4291; 9671</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>20444; 29694</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>19862; 31084</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>18984; 27315</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>9244; 14100</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>29120; 40922</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>37631; 51859</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>32033; 41873</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>15833; 23318</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8784</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3429</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4412</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3900</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7269</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4182</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5891</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>10836</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>10698</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8595</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>9791</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>6051; 10144</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1259; 6105</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1714; 5051</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>617; 4677</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3847; 10315</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2027; 6085</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2193; 7937</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>7513; 13737</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6362; 14521</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5909; 10473</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5791; 12244</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>21408</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25402</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20890</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11718</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>29626</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>41772</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>30392</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>19726</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>51034</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>67174</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>51282</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>31444</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>16940; 26030</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>20223; 31799</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>17772; 22752</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>7852; 14574</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>24310; 34737</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>34579; 48331</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>25073; 34505</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>14805; 22556</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>43009; 57257</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>57634; 76231</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>45684; 56366</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>25883; 35922</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$urgencias-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$urgencias-Estudios-trans_dic.xlsx
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,32; 100,0</t>
+          <t>28,03; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,63; 85,58</t>
+          <t>16,66; 85,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,7; 90,79</t>
+          <t>51,44; 90,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,91; 90,53</t>
+          <t>30,47; 90,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49,48; 85,03</t>
+          <t>48,75; 85,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,08; 65,77</t>
+          <t>30,55; 64,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,29; 66,21</t>
+          <t>38,56; 64,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,91; 96,11</t>
+          <t>66,5; 96,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38,94; 87,77</t>
+          <t>39,38; 87,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55,37; 80,42</t>
+          <t>54,76; 79,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,24; 69,24</t>
+          <t>43,24; 68,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,48; 87,02</t>
+          <t>59,33; 85,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>62,69; 95,62</t>
+          <t>62,57; 95,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,23; 70,59</t>
+          <t>51,09; 71,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,42; 62,6</t>
+          <t>46,4; 63,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66,89; 87,44</t>
+          <t>68,27; 87,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>61,45; 90,5</t>
+          <t>61,26; 90,37</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59,65; 100,0</t>
+          <t>59,12; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,97; 62,89</t>
+          <t>13,7; 66,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,93; 100,0</t>
+          <t>33,58; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,12; 69,15</t>
+          <t>9,1; 64,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,19; 64,88</t>
+          <t>27,36; 68,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,78; 89,42</t>
+          <t>30,3; 90,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,62; 100,0</t>
+          <t>29,17; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44,43; 81,25</t>
+          <t>42,82; 80,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,85; 56,71</t>
+          <t>25,13; 59,7</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52,68; 93,36</t>
+          <t>51,15; 93,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,59; 94,27</t>
+          <t>43,23; 92,42</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,98; 73,73</t>
+          <t>46,15; 72,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,11; 61,49</t>
+          <t>36,98; 60,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,05; 97,36</t>
+          <t>73,31; 96,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,78; 84,98</t>
+          <t>47,07; 85,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,25; 74,66</t>
+          <t>52,74; 74,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,12; 65,87</t>
+          <t>47,51; 66,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,57; 84,73</t>
+          <t>61,89; 84,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61,6; 93,85</t>
+          <t>63,09; 93,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52,56; 69,97</t>
+          <t>53,37; 70,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46,07; 60,94</t>
+          <t>46,54; 60,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71,28; 87,94</t>
+          <t>70,74; 87,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,85; 87,22</t>
+          <t>62,85; 87,16</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1124; 4114</t>
+          <t>1153; 4114</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>674; 3469</t>
+          <t>675; 3479</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6255; 11425</t>
+          <t>6473; 11441</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2566; 6295</t>
+          <t>2119; 6274</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8233; 14147</t>
+          <t>8110; 14282</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6541; 13842</t>
+          <t>6429; 13478</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14533; 25128</t>
+          <t>14634; 24617</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10875; 15858</t>
+          <t>10973; 15850</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4291; 9671</t>
+          <t>4339; 9618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20444; 29694</t>
+          <t>20219; 29441</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19862; 31084</t>
+          <t>19412; 30644</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18984; 27315</t>
+          <t>18625; 26953</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9244; 14100</t>
+          <t>9227; 14126</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29120; 40922</t>
+          <t>29616; 41155</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37631; 51859</t>
+          <t>38444; 52763</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32033; 41873</t>
+          <t>32695; 41789</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15833; 23318</t>
+          <t>15784; 23284</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6051; 10144</t>
+          <t>5998; 10144</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1259; 6105</t>
+          <t>1330; 6465</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1935,47 +1935,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1714; 5051</t>
+          <t>1696; 5051</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>617; 4677</t>
+          <t>615; 4366</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3847; 10315</t>
+          <t>4350; 10818</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2027; 6085</t>
+          <t>2062; 6167</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2193; 7937</t>
+          <t>2315; 7937</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7513; 13737</t>
+          <t>7240; 13673</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6362; 14521</t>
+          <t>6434; 15288</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5909; 10473</t>
+          <t>5738; 10505</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5791; 12244</t>
+          <t>5615; 12004</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16940; 26030</t>
+          <t>16294; 25613</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20223; 31799</t>
+          <t>19123; 31080</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17772; 22752</t>
+          <t>17133; 22651</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7852; 14574</t>
+          <t>8073; 14610</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24310; 34737</t>
+          <t>24536; 34588</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34579; 48331</t>
+          <t>34859; 48560</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25073; 34505</t>
+          <t>25204; 34525</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14805; 22556</t>
+          <t>15164; 22468</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43009; 57257</t>
+          <t>43669; 57426</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>57634; 76231</t>
+          <t>58216; 76037</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45684; 56366</t>
+          <t>45339; 56135</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25883; 35922</t>
+          <t>25886; 35896</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$urgencias-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$urgencias-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>76,33%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>75,19%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>64,03%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>52,13%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>39,74%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>76,33%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>75,19%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>32,81%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>69,05%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>69,57%</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>69,05%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>69,57%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>66,64%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,03; 100,0</t>
+          <t>25,21; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,66; 85,84</t>
+          <t>49,35; 91,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,37 +732,37 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16,52; 100,0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,65; 85,71</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>25,21; 100,0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>51,44; 90,92</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,47; 90,22</t>
+          <t>37,61; 90,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,75; 85,85</t>
+          <t>48,52; 85,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>68,81%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>55,78%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>75,44%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83,77%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>47,47%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>52,33%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>84,98%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>67,05%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>68,81%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>55,78%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>75,44%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,91%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,55; 64,04</t>
+          <t>55,67; 79,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,56; 64,87</t>
+          <t>43,03; 68,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,5; 96,06</t>
+          <t>60,93; 87,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39,38; 87,29</t>
+          <t>59,24; 95,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,76; 79,74</t>
+          <t>30,02; 64,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,24; 68,26</t>
+          <t>39,38; 65,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,33; 85,86</t>
+          <t>66,46; 96,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>62,57; 95,79</t>
+          <t>40,85; 88,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51,09; 71,0</t>
+          <t>50,21; 70,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46,4; 63,69</t>
+          <t>45,52; 62,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68,27; 87,26</t>
+          <t>67,53; 87,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>61,26; 90,37</t>
+          <t>60,21; 88,47</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>30,35%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>45,72%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>61,46%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>73,19%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>86,59%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>35,32%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>77,21%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>30,35%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45,72%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>61,46%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59,12; 100,0</t>
+          <t>8,94; 61,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,7; 66,59</t>
+          <t>25,35; 66,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>24,12; 90,74</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>28,78; 100,0</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>61,79; 100,0</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>13,34; 62,59</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>33,58; 100,0</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>9,1; 64,54</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>27,36; 68,04</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>30,3; 90,63</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,17; 100,0</t>
+          <t>36,43; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42,82; 80,86</t>
+          <t>45,02; 81,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,13; 59,7</t>
+          <t>26,8; 57,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,15; 93,65</t>
+          <t>51,45; 94,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43,23; 92,42</t>
+          <t>45,77; 94,08</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>63,68%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56,93%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>74,63%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>81,09%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>60,64%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>49,12%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>89,39%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>68,32%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>63,68%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>74,63%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,15; 72,55</t>
+          <t>51,93; 74,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,98; 60,1</t>
+          <t>46,34; 66,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,31; 96,93</t>
+          <t>61,69; 84,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47,07; 85,19</t>
+          <t>60,56; 93,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,74; 74,34</t>
+          <t>47,21; 71,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,51; 66,18</t>
+          <t>38,36; 60,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,89; 84,78</t>
+          <t>74,54; 97,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63,09; 93,49</t>
+          <t>48,84; 85,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53,37; 70,18</t>
+          <t>53,35; 70,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46,54; 60,79</t>
+          <t>45,56; 60,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70,74; 87,58</t>
+          <t>69,61; 86,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,85; 87,16</t>
+          <t>61,46; 85,56</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,32 +1368,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2167</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9462</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2634</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2113</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2457</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2167</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9462</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>369</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1510</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1153; 4114</t>
+          <t>716; 2839</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>675; 3479</t>
+          <t>6210; 11524</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1519,17 +1519,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1082</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>716; 2839</t>
+          <t>680; 4114</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6473; 11441</t>
+          <t>675; 3474</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1539,27 +1539,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>0; 1125</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2615; 6284</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>8072; 14287</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2119; 6274</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8110; 14282</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2432</t>
+          <t>0; 2266</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>25406</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>25041</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23681</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9990</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>19861</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>14021</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7388</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>25406</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25041</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23681</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>19013</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6429; 13478</t>
+          <t>20556; 29449</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14634; 24617</t>
+          <t>19318; 30546</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10973; 15850</t>
+          <t>19127; 27365</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4339; 9618</t>
+          <t>8134; 13108</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20219; 29441</t>
+          <t>6317; 13554</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19412; 30644</t>
+          <t>14944; 24798</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18625; 26953</t>
+          <t>10966; 15841</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9227; 14126</t>
+          <t>4490; 9723</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29616; 41155</t>
+          <t>29103; 41054</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38444; 52763</t>
+          <t>37713; 51995</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32695; 41789</t>
+          <t>32342; 41746</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15784; 23284</t>
+          <t>14884; 21870</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7269</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4182</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5403</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>8784</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3429</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4412</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3900</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2053</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7269</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4182</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>9437</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5998; 10144</t>
+          <t>605; 4177</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1330; 6465</t>
+          <t>4031; 10502</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>1641; 6175</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2125; 7382</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6268; 10144</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1295; 6076</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1696; 5051</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>615; 4366</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4350; 10818</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2062; 6167</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2315; 7937</t>
+          <t>1846; 5068</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7240; 13673</t>
+          <t>7611; 13717</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6434; 15288</t>
+          <t>6862; 14808</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5738; 10505</t>
+          <t>5772; 10586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5615; 12004</t>
+          <t>5698; 11712</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>29626</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>41772</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>30392</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18044</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>21408</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>25402</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>20890</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11718</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>29626</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>41772</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>30392</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>29960</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16294; 25613</t>
+          <t>24159; 34526</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19123; 31080</t>
+          <t>34003; 48513</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17133; 22651</t>
+          <t>25123; 34515</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8073; 14610</t>
+          <t>13475; 20795</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24536; 34588</t>
+          <t>16668; 25410</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34859; 48560</t>
+          <t>19839; 31517</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25204; 34525</t>
+          <t>17420; 22702</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15164; 22468</t>
+          <t>8392; 14651</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43669; 57426</t>
+          <t>43659; 57555</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58216; 76037</t>
+          <t>56997; 75948</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45339; 56135</t>
+          <t>44615; 55531</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25886; 35896</t>
+          <t>24237; 33742</t>
         </is>
       </c>
     </row>
